--- a/Design/Excel/ET/Datas/StartConfig/StartProcessConfig.xlsx
+++ b/Design/Excel/ET/Datas/StartConfig/StartProcessConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="StartProcessConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="16">
   <si>
     <t>##var</t>
   </si>
@@ -1079,12 +1079,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="12.75" style="2" customWidth="1"/>
-    <col min="4" max="5" width="12.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="3" width="12.7545454545455" style="2" customWidth="1"/>
+    <col min="4" max="5" width="12.6272727272727" style="3" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1139,7 +1139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:5">
       <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>20001</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:5">
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1245,132 +1245,132 @@
     <row r="11" s="1" customFormat="1" spans="1:5">
       <c r="A11" s="2"/>
       <c r="B11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6">
+        <v>100001</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6">
+        <v>21001</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:5">
+      <c r="A12" s="2"/>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6">
+        <v>100002</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>21002</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:5">
+      <c r="A13" s="2"/>
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6">
         <v>20001</v>
       </c>
     </row>
-    <row r="12" spans="2:5">
-      <c r="B12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6">
-        <v>20001</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
-        <v>20002</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+    <row r="14" s="1" customFormat="1" spans="1:5">
+      <c r="A14" s="2"/>
       <c r="B14" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6">
-        <v>3</v>
+        <v>100001</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
       </c>
       <c r="E14" s="6">
-        <v>20003</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <v>21001</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:5">
+      <c r="A15" s="2"/>
       <c r="B15" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="6">
-        <v>4</v>
+        <v>100002</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
       </c>
       <c r="E15" s="6">
-        <v>20004</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:5">
-      <c r="A16" s="2"/>
+        <v>21002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="B16" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
       </c>
       <c r="E16" s="6">
-        <v>20005</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:5">
-      <c r="A17" s="2"/>
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" s="6">
         <v>1</v>
       </c>
       <c r="E17" s="6">
-        <v>20006</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:5">
-      <c r="A18" s="2"/>
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6">
         <v>1</v>
       </c>
       <c r="E18" s="6">
-        <v>20007</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:5">
-      <c r="A19" s="2"/>
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
       </c>
       <c r="E19" s="6">
-        <v>20008</v>
+        <v>20004</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:5">
@@ -1379,13 +1379,13 @@
         <v>14</v>
       </c>
       <c r="C20" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
       </c>
       <c r="E20" s="6">
-        <v>20009</v>
+        <v>20005</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:5">
@@ -1394,13 +1394,13 @@
         <v>14</v>
       </c>
       <c r="C21" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
       </c>
       <c r="E21" s="6">
-        <v>20010</v>
+        <v>20006</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:5">
@@ -1409,13 +1409,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="6">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
       </c>
       <c r="E22" s="6">
-        <v>20011</v>
+        <v>20007</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:5">
@@ -1424,117 +1424,235 @@
         <v>14</v>
       </c>
       <c r="C23" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
       </c>
       <c r="E23" s="6">
-        <v>20012</v>
+        <v>20008</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:5">
       <c r="A24" s="2"/>
       <c r="B24" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
       </c>
       <c r="E24" s="6">
-        <v>20001</v>
+        <v>20009</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:5">
       <c r="A25" s="2"/>
       <c r="B25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="3">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="C25" s="6">
+        <v>10</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
       </c>
       <c r="E25" s="6">
-        <v>20002</v>
+        <v>20010</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="3">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="C26" s="6">
+        <v>11</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
       </c>
       <c r="E26" s="6">
-        <v>20003</v>
+        <v>20011</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="3">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="C27" s="6">
+        <v>12</v>
       </c>
       <c r="D27" s="6">
         <v>1</v>
       </c>
       <c r="E27" s="6">
-        <v>20004</v>
+        <v>20012</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="3">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="C28" s="6">
+        <v>100001</v>
       </c>
       <c r="D28" s="6">
         <v>1</v>
       </c>
       <c r="E28" s="6">
-        <v>20005</v>
+        <v>21001</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="3">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="C29" s="6">
+        <v>100002</v>
       </c>
       <c r="D29" s="6">
         <v>1</v>
       </c>
       <c r="E29" s="6">
-        <v>20006</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" spans="2:5">
+        <v>21002</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:5">
+      <c r="A30" s="2"/>
       <c r="B30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>20001</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>20002</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:5">
+      <c r="A32" s="2"/>
+      <c r="B32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="3">
+        <v>3</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6">
+        <v>20003</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:5">
+      <c r="A33" s="2"/>
+      <c r="B33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="3">
+        <v>4</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6">
+        <v>20004</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="3">
+        <v>5</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6">
+        <v>20005</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:5">
+      <c r="A35" s="2"/>
+      <c r="B35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="3">
+        <v>6</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>20006</v>
+      </c>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:5">
+      <c r="B36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="3">
         <v>7</v>
       </c>
-      <c r="D30" s="6">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6">
+      <c r="D36" s="6">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6">
         <v>20007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="B37" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="6">
+        <v>100001</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6">
+        <v>21001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="B38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="6">
+        <v>100002</v>
+      </c>
+      <c r="D38" s="6">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6">
+        <v>21002</v>
       </c>
     </row>
   </sheetData>
